--- a/data/dividends_info_20260804.xlsx
+++ b/data/dividends_info_20260804.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>46.25500106811523</v>
+        <v>46.88999938964844</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1945735551221062</v>
+        <v>0.1919385821529113</v>
       </c>
       <c r="J2" t="n">
         <v>223</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>66.59999847412109</v>
+        <v>67.19999694824219</v>
       </c>
       <c r="I3" t="n">
-        <v>1.051051075131782</v>
+        <v>1.041666713971942</v>
       </c>
       <c r="J3" t="n">
         <v>202</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9.199999809265137</v>
+        <v>9.180000305175781</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6521739265643809</v>
+        <v>0.6535947495140209</v>
       </c>
       <c r="J4" t="n">
         <v>132</v>
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.4740000069141388</v>
+        <v>0.4600000083446503</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8438818442305566</v>
+        <v>0.8695652016169185</v>
       </c>
       <c r="J5" t="n">
         <v>132</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>46.2400016784668</v>
+        <v>46.88999938964844</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1946366711355711</v>
+        <v>0.1919385821529113</v>
       </c>
       <c r="J6" t="n">
         <v>132</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.134999990463257</v>
+        <v>2.150000095367432</v>
       </c>
       <c r="I7" t="n">
-        <v>3.606557393159162</v>
+        <v>3.58139518997746</v>
       </c>
       <c r="J7" t="n">
         <v>111</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>24.10000038146973</v>
+        <v>23.25</v>
       </c>
       <c r="I8" t="n">
-        <v>1.120331932474161</v>
+        <v>1.161290322580645</v>
       </c>
       <c r="J8" t="n">
         <v>111</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5.949999809265137</v>
+        <v>5.960000038146973</v>
       </c>
       <c r="I9" t="n">
-        <v>3.36134464556733</v>
+        <v>3.355704676508394</v>
       </c>
       <c r="J9" t="n">
         <v>104</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>7.699999809265137</v>
+        <v>7.900000095367432</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7792207985226717</v>
+        <v>0.7594936617175999</v>
       </c>
       <c r="J10" t="n">
         <v>76</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.4740000069141388</v>
+        <v>0.4600000083446503</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8438818442305566</v>
+        <v>0.8695652016169185</v>
       </c>
       <c r="J11" t="n">
         <v>76</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>5.059999942779541</v>
+        <v>5.079999923706055</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7509881507849578</v>
+        <v>0.7480315072972982</v>
       </c>
       <c r="J13" t="n">
         <v>55</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>24.10000038146973</v>
+        <v>23.25</v>
       </c>
       <c r="I14" t="n">
-        <v>1.120331932474161</v>
+        <v>1.161290322580645</v>
       </c>
       <c r="J14" t="n">
         <v>48</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1.968000054359436</v>
+        <v>1.998000025749207</v>
       </c>
       <c r="I15" t="n">
-        <v>2.896341383412864</v>
+        <v>2.852852816086739</v>
       </c>
       <c r="J15" t="n">
         <v>48</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>46.2400016784668</v>
+        <v>46.88999938964844</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1946366711355711</v>
+        <v>0.1919385821529113</v>
       </c>
       <c r="J16" t="n">
         <v>48</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>95.34999847412109</v>
+        <v>97.34999847412109</v>
       </c>
       <c r="I17" t="n">
-        <v>1.394861060601878</v>
+        <v>1.366204438465974</v>
       </c>
       <c r="J17" t="n">
         <v>48</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>5.78000020980835</v>
+        <v>5.699999809265137</v>
       </c>
       <c r="I18" t="n">
-        <v>5.190311230281897</v>
+        <v>5.263158070853988</v>
       </c>
       <c r="J18" t="n">
         <v>41</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>0.4740000069141388</v>
+        <v>0.4600000083446503</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8438818442305566</v>
+        <v>0.8695652016169185</v>
       </c>
       <c r="J19" t="n">
         <v>20</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>5.059999942779541</v>
+        <v>5.079999923706055</v>
       </c>
       <c r="I21" t="n">
-        <v>0.7509881507849578</v>
+        <v>0.7480315072972982</v>
       </c>
       <c r="J21" t="n">
         <v>-1</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>2.839999914169312</v>
+        <v>2.829999923706055</v>
       </c>
       <c r="I23" t="n">
-        <v>5.210176213800356</v>
+        <v>5.228586713395586</v>
       </c>
       <c r="J23" t="n">
         <v>-1</v>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>5.78000020980835</v>
+        <v>5.769999980926514</v>
       </c>
       <c r="I24" t="n">
-        <v>4.325259358568248</v>
+        <v>4.33275564690481</v>
       </c>
       <c r="J24" t="n">
         <v>-8</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>4.099999904632568</v>
+        <v>4.119999885559082</v>
       </c>
       <c r="I25" t="n">
-        <v>3.414634225767048</v>
+        <v>3.398058346814786</v>
       </c>
       <c r="J25" t="n">
         <v>-15</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>10.02000045776367</v>
+        <v>9.994999885559082</v>
       </c>
       <c r="I26" t="n">
-        <v>2.594810260697618</v>
+        <v>2.601300680109579</v>
       </c>
       <c r="J26" t="n">
         <v>-15</v>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>13.61999988555908</v>
+        <v>13.72000026702881</v>
       </c>
       <c r="I27" t="n">
-        <v>4.405286380627387</v>
+        <v>4.373177757451571</v>
       </c>
       <c r="J27" t="n">
         <v>-15</v>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>2.657999992370605</v>
+        <v>2.654000043869019</v>
       </c>
       <c r="I28" t="n">
-        <v>8.276899948513067</v>
+        <v>8.289374391994455</v>
       </c>
       <c r="J28" t="n">
         <v>-15</v>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>0.4740000069141388</v>
+        <v>0.4600000083446503</v>
       </c>
       <c r="I29" t="n">
-        <v>0.8438818442305566</v>
+        <v>0.8695652016169185</v>
       </c>
       <c r="J29" t="n">
         <v>-15</v>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>6.534999847412109</v>
+        <v>6.630000114440918</v>
       </c>
       <c r="I30" t="n">
-        <v>3.672532602966182</v>
+        <v>3.61990943977892</v>
       </c>
       <c r="J30" t="n">
         <v>-15</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>18.64999961853027</v>
+        <v>18.60000038146973</v>
       </c>
       <c r="I31" t="n">
-        <v>2.016085832122022</v>
+        <v>2.02150533488478</v>
       </c>
       <c r="J31" t="n">
         <v>-15</v>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>5.659999847412109</v>
+        <v>5.670000076293945</v>
       </c>
       <c r="I33" t="n">
-        <v>2.120141399913057</v>
+        <v>2.116402087924397</v>
       </c>
       <c r="J33" t="n">
         <v>-22</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>8.649999618530273</v>
+        <v>9</v>
       </c>
       <c r="I34" t="n">
-        <v>0.5780347075725714</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="J34" t="n">
         <v>-22</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>3</v>
+        <v>3.019999980926514</v>
       </c>
       <c r="I35" t="n">
-        <v>5</v>
+        <v>4.966887448588033</v>
       </c>
       <c r="J35" t="n">
         <v>-22</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>38.15000152587891</v>
+        <v>38</v>
       </c>
       <c r="I38" t="n">
-        <v>0.3931847811283783</v>
+        <v>0.3947368421052632</v>
       </c>
       <c r="J38" t="n">
         <v>-29</v>
@@ -3587,129 +3587,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>LANDI RENZO S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>PININFARINA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Sanlorenzo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>iVision Tech S.p.A.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>